--- a/naver-place-crawler/results_health/중구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/중구_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -624,10 +624,10 @@
         <v>1056</v>
       </c>
       <c r="Q2" t="n">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="R2" t="n">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>빌드업피트니스 PT&amp;골프 서대문역점</t>
+          <t>스포애니 서울시청역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>buildupfitness06@naver.com</t>
+          <t>spoany_73@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1325-6473</t>
+          <t>0507-1335-5273</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 중구 통일로 86 지하층 101호, 102호, 103호</t>
+          <t>서울특별시 중구 서소문로 124 씨티스퀘어 B2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://buildupfitness.co.kr/</t>
+          <t>https://blog.naver.com/spoany_73</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1491</v>
+        <v>918</v>
       </c>
       <c r="Q4" t="n">
-        <v>884</v>
+        <v>1810</v>
       </c>
       <c r="R4" t="n">
-        <v>2375</v>
+        <v>2728</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1502740692</t>
+          <t>1394113072</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1502740692</t>
+          <t>https://m.place.naver.com/place/1394113072</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포애니 서울시청역점</t>
+          <t>빌드업피트니스 PT&amp;골프 서대문역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spoany_73@naver.com</t>
+          <t>buildupfitness06@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1335-5273</t>
+          <t>0507-1325-6473</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 124 씨티스퀘어 B2층</t>
+          <t>서울특별시 중구 통일로 86 지하층 101호, 102호, 103호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_73</t>
+          <t>https://buildupfitness.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>918</v>
+        <v>1491</v>
       </c>
       <c r="Q6" t="n">
-        <v>1807</v>
+        <v>884</v>
       </c>
       <c r="R6" t="n">
-        <v>2725</v>
+        <v>2375</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1394113072</t>
+          <t>1502740692</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394113072</t>
+          <t>https://m.place.naver.com/place/1502740692</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>짐구공 헬스 PT 골프 광화문점</t>
+          <t>바벨피트니스 PT &amp; 바렐필라테스 은행동점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sujjong1015@naver.com</t>
+          <t>barbellf07@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1389-0825</t>
+          <t>0507-1466-6683</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 중구 무교로 16 9층, 10층</t>
+          <t>대전 중구 중앙로164번길 22-12 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://buly.kr/613HU8T</t>
+          <t>https://blog.naver.com/barbellf07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1080,10 +1080,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uuci</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>502</v>
+        <v>1154</v>
       </c>
       <c r="Q7" t="n">
-        <v>723</v>
+        <v>199</v>
       </c>
       <c r="R7" t="n">
-        <v>1225</v>
+        <v>1353</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1114,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1816876645</t>
+          <t>1141342986</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816876645</t>
+          <t>https://m.place.naver.com/place/1141342986</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1132,29 +1136,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MCTGYM 헬스&amp;PT 장충</t>
+          <t>짐구공 헬스 PT 요가이서 시청역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mctfitness6@naver.com</t>
+          <t>gym90_cityhallst@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1390-7537</t>
+          <t>0507-1474-0487</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울 중구 장충단로 187 3층</t>
+          <t>서울특별시 중구 서소문로 115 1층 102호, 103호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://mctgym.com/</t>
+          <t>https://gym90.creatorlink.net/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,19 +1173,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wtebelj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1193,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>35</v>
+        <v>1132</v>
       </c>
       <c r="Q8" t="n">
-        <v>60</v>
+        <v>1487</v>
       </c>
       <c r="R8" t="n">
-        <v>95</v>
+        <v>2619</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,51 +1208,35 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1534618598</t>
+          <t>1107768782</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1534618598</t>
+          <t>https://m.place.naver.com/place/1107768782</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>세심한 피티 스튜디오</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>kmg09302@naver.com</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1422-3416</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 중구 퇴계로 409 흥인빌딩 3층</t>
+          <t>주소</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pt_careful</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1262,7 +1246,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1272,14 +1256,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs0n4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1287,17 +1267,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1163442521</t>
+          <t>11413429</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163442521</t>
+          <t>https://m.place.naver.com/place/11413429</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1328,34 +1308,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>원샵PT</t>
+          <t>마이크로스튜디오 시청점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6222406a@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>cityhallmicro@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>owner@microstudio.kr</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-2883</t>
+          <t>0507-1346-2162</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 중구 다산로18길 23 1층 원샵</t>
+          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_oneshop_official</t>
+          <t>https://microstudio.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1365,22 +1349,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yv69</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1389,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="Q10" t="n">
-        <v>366</v>
+        <v>744</v>
       </c>
       <c r="R10" t="n">
-        <v>598</v>
+        <v>983</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,17 +1384,115 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1045206951</t>
+          <t>1381838006</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1045206951</t>
+          <t>https://m.place.naver.com/place/1381838006</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>세심한 피티 스튜디오</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>kmg09302@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1422-3416</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>서울 중구 퇴계로 409 흥인빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pt_careful</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcs0n4</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>97</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1163442521</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1163442521</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/중구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/중구_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="Q2" t="n">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="R2" t="n">
-        <v>2669</v>
+        <v>2672</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -752,29 +752,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포애니 서울시청역점</t>
+          <t>버핏그라운드 광화문</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>spoany_73@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1335-5273</t>
+          <t>0507-1314-3624</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 124 씨티스퀘어 B2층</t>
+          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_73</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -800,22 +804,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>918</v>
+        <v>294</v>
       </c>
       <c r="Q4" t="n">
-        <v>1810</v>
+        <v>396</v>
       </c>
       <c r="R4" t="n">
-        <v>2728</v>
+        <v>690</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1394113072</t>
+          <t>1720388209</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394113072</t>
+          <t>https://m.place.naver.com/place/1720388209</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,33 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>버핏그라운드 광화문</t>
+          <t>스포애니 서울시청역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>spoany_73@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1314-3624</t>
+          <t>0507-1335-5273</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
+          <t>서울특별시 중구 서소문로 124 씨티스퀘어 B2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://blog.naver.com/spoany_73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -898,22 +898,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>292</v>
+        <v>920</v>
       </c>
       <c r="Q5" t="n">
-        <v>388</v>
+        <v>1812</v>
       </c>
       <c r="R5" t="n">
-        <v>680</v>
+        <v>2732</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1720388209</t>
+          <t>1394113072</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720388209</t>
+          <t>https://m.place.naver.com/place/1394113072</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>빌드업피트니스 PT&amp;골프 서대문역점</t>
+          <t>짐구공 헬스 PT 골프 광화문점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>buildupfitness06@naver.com</t>
+          <t>sujjong1015@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1325-6473</t>
+          <t>0507-1389-0825</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 중구 통일로 86 지하층 101호, 102호, 103호</t>
+          <t>서울특별시 중구 무교로 16 9층, 10층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://buildupfitness.co.kr/</t>
+          <t>https://buly.kr/613HU8T</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1491</v>
+        <v>502</v>
       </c>
       <c r="Q6" t="n">
-        <v>884</v>
+        <v>723</v>
       </c>
       <c r="R6" t="n">
-        <v>2375</v>
+        <v>1225</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1502740692</t>
+          <t>1816876645</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1502740692</t>
+          <t>https://m.place.naver.com/place/1816876645</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바벨피트니스 PT &amp; 바렐필라테스 은행동점</t>
+          <t>모던 휘트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>barbellf07@naver.com</t>
+          <t>mr2416_@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1466-6683</t>
+          <t>0507-1375-2416</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전 중구 중앙로164번길 22-12 3층</t>
+          <t>대전 중구 목중로 22 2층,3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barbellf07</t>
+          <t>https://blog.naver.com/mr2416_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5uuci</t>
+          <t>https://talk.naver.com/ct/wqu7g29</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1154</v>
+        <v>61</v>
       </c>
       <c r="Q7" t="n">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="R7" t="n">
-        <v>1353</v>
+        <v>242</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1141342986</t>
+          <t>1966964430</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141342986</t>
+          <t>https://m.place.naver.com/place/1966964430</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1131,34 +1131,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>짐구공 헬스 PT 요가이서 시청역점</t>
+          <t>버핏그라운드 PT 광화문</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gym90_cityhallst@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1474-0487</t>
+          <t>0507-1413-0755</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 115 1층 102호, 103호</t>
+          <t>서울특별시 중구 세종대로 136 서울파이낸스센터 SFC B1, B2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://gym90.creatorlink.net/</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1173,7 +1177,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1184,7 +1188,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1193,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1132</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1487</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>2619</v>
+        <v>1</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1212,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1107768782</t>
+          <t>2093030344</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107768782</t>
+          <t>https://m.place.naver.com/place/2093030344</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1223,20 +1227,36 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>세심한 피티 스튜디오</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>kmg09302@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1422-3416</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>주소</t>
+          <t>서울 중구 퇴계로 409 흥인빌딩 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/pt_careful</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1246,7 +1266,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1256,10 +1276,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcs0n4</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1267,17 +1291,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1310,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>11413429</t>
+          <t>1163442521</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11413429</t>
+          <t>https://m.place.naver.com/place/1163442521</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1308,38 +1332,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마이크로스튜디오 시청점</t>
+          <t>원샵PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cityhallmicro@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>owner@microstudio.kr</t>
-        </is>
-      </c>
+          <t>6222406a@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1346-2162</t>
+          <t>0507-1359-2883</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
+          <t>서울 중구 다산로18길 23 1층 원샵</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://microstudio.kr</t>
+          <t>https://www.instagram.com/_oneshop_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1349,18 +1369,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yv69</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q10" t="n">
-        <v>744</v>
+        <v>366</v>
       </c>
       <c r="R10" t="n">
-        <v>983</v>
+        <v>598</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,113 +1408,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1381838006</t>
+          <t>1045206951</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1381838006</t>
+          <t>https://m.place.naver.com/place/1045206951</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>세심한 피티 스튜디오</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>kmg09302@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1422-3416</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>서울 중구 퇴계로 409 흥인빌딩 3층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/pt_careful</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs0n4</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>90</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7</v>
-      </c>
-      <c r="R11" t="n">
-        <v>97</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1163442521</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1163442521</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/중구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/중구_헬스장.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -624,10 +624,10 @@
         <v>1057</v>
       </c>
       <c r="Q2" t="n">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="R2" t="n">
-        <v>2672</v>
+        <v>2674</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -816,10 +816,10 @@
         <v>294</v>
       </c>
       <c r="Q4" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R4" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1124,45 +1124,37 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 광화문</t>
+          <t>팀버핏 광화문</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1413-0755</t>
-        </is>
-      </c>
+          <t>jhjh5508@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 서울파이낸스센터 SFC B1, B2층</t>
+          <t>서울특별시 중구 세종대로 136 지하 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://www.teambutfit.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1188,7 +1180,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1197,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>274</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,56 +1204,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2093030344</t>
+          <t>1117727301</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093030344</t>
+          <t>https://m.place.naver.com/place/1117727301</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>세심한 피티 스튜디오</t>
+          <t>짐구공 헬스 PT 요가이서 시청역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kmg09302@naver.com</t>
+          <t>gym90_cityhallst@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1422-3416</t>
+          <t>0507-1474-0487</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 중구 퇴계로 409 흥인빌딩 3층</t>
+          <t>서울특별시 중구 서소문로 115 1층 102호, 103호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pt_careful</t>
+          <t>https://gym90.creatorlink.net/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1276,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcs0n4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1295,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>90</v>
+        <v>1134</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>1490</v>
       </c>
       <c r="R9" t="n">
-        <v>97</v>
+        <v>2624</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1163442521</t>
+          <t>1107768782</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163442521</t>
+          <t>https://m.place.naver.com/place/1107768782</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1332,34 +1320,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>원샵PT</t>
+          <t>마이크로스튜디오 시청점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6222406a@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>cityhallmicro@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>owner@microstudio.kr</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1359-2883</t>
+          <t>0507-1346-2162</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울 중구 다산로18길 23 1층 원샵</t>
+          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_oneshop_official</t>
+          <t>https://microstudio.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1369,22 +1361,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yv69</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1393,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="Q10" t="n">
-        <v>366</v>
+        <v>745</v>
       </c>
       <c r="R10" t="n">
-        <v>598</v>
+        <v>984</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,17 +1396,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1045206951</t>
+          <t>1381838006</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1045206951</t>
+          <t>https://m.place.naver.com/place/1381838006</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/중구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/중구_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>짐구공 24시 헬스 PT 시청점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gym90_cityhall@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1313-9682</t>
+          <t>070-4572-4677</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 64 2층 210호</t>
+          <t>서울특별시 중구 삼각동</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gym90_cityhall/224137563110</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1057</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1617</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2674</v>
+        <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1521560652</t>
+          <t>1014405536</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1521560652</t>
+          <t>https://m.place.naver.com/place/1014405536</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,39 +658,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FITNESS101 명동점</t>
+          <t>더 플라자 피트니스 클럽</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fitness101@naver.com</t>
+          <t>wjddma201@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1345-0124</t>
+          <t>02-771-2200</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 중구 삼일대로 343 대신파이낸스센터 지하2층</t>
+          <t>서울특별시 중구 소공로 119</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://fitness101-vrtour.netlify.app/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1018</v>
+        <v>46</v>
       </c>
       <c r="Q3" t="n">
-        <v>1261</v>
+        <v>16</v>
       </c>
       <c r="R3" t="n">
-        <v>2279</v>
+        <v>62</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1025105266</t>
+          <t>1097314721</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1025105266</t>
+          <t>https://m.place.naver.com/place/1097314721</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -752,33 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>버핏그라운드 광화문</t>
+          <t>은행회관 헬스클럽</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>osbum1478@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1314-3624</t>
+          <t>02-3705-5382</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
+          <t>서울특별시 중구 명동11길 19</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +784,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -804,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>294</v>
+        <v>100</v>
       </c>
       <c r="Q4" t="n">
-        <v>397</v>
+        <v>22</v>
       </c>
       <c r="R4" t="n">
-        <v>691</v>
+        <v>122</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1720388209</t>
+          <t>30844087</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1720388209</t>
+          <t>https://m.place.naver.com/place/30844087</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -850,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포애니 서울시청역점</t>
+          <t>짐구공 헬스 PT 요가이서 시청역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>spoany_73@naver.com</t>
+          <t>gym90_cityhallst@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1335-5273</t>
+          <t>0507-1474-0487</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 124 씨티스퀘어 B2층</t>
+          <t>서울특별시 중구 서소문로 115 1층 102호, 103호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_73</t>
+          <t>https://gym90.creatorlink.net/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -887,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>920</v>
+        <v>1134</v>
       </c>
       <c r="Q5" t="n">
-        <v>1812</v>
+        <v>1492</v>
       </c>
       <c r="R5" t="n">
-        <v>2732</v>
+        <v>2626</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1394113072</t>
+          <t>1107768782</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394113072</t>
+          <t>https://m.place.naver.com/place/1107768782</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>짐구공 헬스 PT 골프 광화문점</t>
+          <t>센터원웰니스 을지로점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sujjong1015@naver.com</t>
+          <t>2011wellness@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1389-0825</t>
+          <t>0507-1346-1002</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 중구 무교로 16 9층, 10층</t>
+          <t>서울특별시 중구 을지로5길 26 미래에셋 센터원 서관 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://buly.kr/613HU8T</t>
+          <t>http://www.center1wellness.com</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -992,7 +988,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1001,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="Q6" t="n">
-        <v>723</v>
+        <v>388</v>
       </c>
       <c r="R6" t="n">
-        <v>1225</v>
+        <v>884</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1816876645</t>
+          <t>1245524419</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816876645</t>
+          <t>https://m.place.naver.com/place/1245524419</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1034,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>모던 휘트니스</t>
+          <t>우리헬스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mr2416_@naver.com</t>
+          <t>bus6719@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1375-2416</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전 중구 목중로 22 2층,3층</t>
+          <t>서울특별시 중구 소공로 51</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mr2416_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,24 +1062,20 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wqu7g29</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,17 +1083,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="n">
-        <v>181</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>242</v>
+        <v>58</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,57 +1102,61 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1966964430</t>
+          <t>1539218850</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966964430</t>
+          <t>https://m.place.naver.com/place/1539218850</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>팀버핏 광화문</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jhjh5508@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>070-8956-5260</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 136 지하 1층</t>
+          <t>서울특별시 중구 을지로1가</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.teambutfit.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1185,17 +1177,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1117727301</t>
+          <t>1517783400</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117727301</t>
+          <t>https://m.place.naver.com/place/1517783400</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1226,34 +1218,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>짐구공 헬스 PT 요가이서 시청역점</t>
+          <t>파크짐 동대문점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gym90_cityhallst@naver.com</t>
+          <t>parkgym12@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1474-0487</t>
+          <t>0507-1323-2890</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 중구 서소문로 115 1층 102호, 103호</t>
+          <t>서울특별시 중구 퇴계로 307 B1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://gym90.creatorlink.net/</t>
+          <t>https://blog.naver.com/parkgym12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1263,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1283,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1134</v>
+        <v>1392</v>
       </c>
       <c r="Q9" t="n">
-        <v>1490</v>
+        <v>1186</v>
       </c>
       <c r="R9" t="n">
-        <v>2624</v>
+        <v>2578</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,70 +1290,66 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1107768782</t>
+          <t>1599710112</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107768782</t>
+          <t>https://m.place.naver.com/place/1599710112</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마이크로스튜디오 시청점</t>
+          <t>호텔롯데 휘트니스클럽</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cityhallmicro@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>owner@microstudio.kr</t>
-        </is>
-      </c>
+          <t>nrufree@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1346-2162</t>
+          <t>02-317-7305</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
+          <t>서울특별시 중구 을지로 30</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://microstudio.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1372,41 +1360,8309 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>21</v>
+      </c>
+      <c r="R10" t="n">
+        <v>24</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>77278594</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/77278594</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MCTGYM 헬스&amp;PT 장충</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mctfitness6@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1390-7537</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 187 3층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://mctgym.com/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>60</v>
+      </c>
+      <c r="R11" t="n">
+        <v>95</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1534618598</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1534618598</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>짐구공 24시 헬스 PT 시청점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gym90_cityhall@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1313-9682</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로 64 2층 210호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gym90_cityhall/224137563110</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1061</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1624</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2685</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1521560652</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1521560652</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MCTGYM 서울시청점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>mctfitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1428-3676</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로9길 40 지하1층 MCTGYM 서울시청점</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://youtube.com/https://@mct12</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>466</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>499</v>
+      </c>
+      <c r="R13" t="n">
+        <v>965</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1610785803</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1610785803</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>070-8956-7924</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 삼각동</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1800136190</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1800136190</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>샤머니짐 헬스&amp;PT 동대문점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>resort_14@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1424-7205</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 264 6층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/resort_14</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>530</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>500</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1030</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1075549287</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1075549287</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GR피트니스</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>osbum1478@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로 14 그랜드센트럴 3층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>53</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1028238593</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1028238593</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>명동바디플렉스짐 헬스&amp;PT 명동본점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bodyflex@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1333-4477</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 97</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bodyflex</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1476</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>37647987</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37647987</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>파크짐 서울역점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>parkgym1872-@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1347-1872</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 칠패로 42 지하 1층 파크짐</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/parkgym1872-/224205775300</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>1142</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>697</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1839</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>36391240</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36391240</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>070-4594-2155</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 수표동</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1207354572</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1207354572</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>트리니티을지베이스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gymsh1982@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>02-365-7737</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로 360 비1층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2072308074</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2072308074</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>빌드업피트니스 PT&amp;골프 서대문역점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>buildupfitness06@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1325-6473</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 통일로 86 지하층 101호, 102호, 103호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://buildupfitness.co.kr/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>1501</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>885</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2386</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1502740692</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1502740692</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>스포애니 서울시청역점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>spoany_73@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1335-5273</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 서소문로 124 씨티스퀘어 B2층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany_73</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>922</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1811</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2733</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1394113072</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1394113072</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>070-8956-8030</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로1가</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1235434022</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1235434022</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>어반서울스쿼시 시청점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>seoulsquash8@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1325-6209</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 서소문로 115 지하1층 109호, 114호, 115호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/seoulsquash8</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>103</v>
+      </c>
+      <c r="R24" t="n">
+        <v>215</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1036521616</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1036521616</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UNO GYM</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>unogym_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1347-5567</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 32 제5상가 101호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/unogymstore</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>22</v>
+      </c>
+      <c r="R25" t="n">
+        <v>27</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1143142459</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1143142459</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>070-4594-4698</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로1가</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1150380300</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1150380300</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>온핏스마트짐 을지트윈타워점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>onfit_eulji@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 170 을지트윈타워 동관 3F 301-4 온핏스마트짐</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/onfit_eulji</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>182</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>228</v>
+      </c>
+      <c r="R27" t="n">
+        <v>410</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1204148756</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1204148756</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>070-4594-0530</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 소공동</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1410781538</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1410781538</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>알티오휘트니스</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>altiofitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1301-6749</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 32 스포츠센터동 2층 204호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/altiofitness</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>17</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2030256553</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2030256553</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>헬스보이짐앤필라걸 서울시청점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>healthboy52@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1345-4222</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 무교로 21 지하1층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/healthboy52/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>1019</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1262</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2281</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1954406967</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1954406967</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>충무로 주짓수 PT 헬스 러쉬클랜</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>rushclancmr@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1444-8829</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 서애로1길 10 3층, 4층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rushclancmr</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>193</v>
+      </c>
+      <c r="R31" t="n">
+        <v>223</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1348009048</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1348009048</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>버핏그라운드 광화문</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1314-3624</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로 136 B1, B2층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://pt.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>294</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>407</v>
+      </c>
+      <c r="R32" t="n">
+        <v>701</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1720388209</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1720388209</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>센트럴골프헬스요가</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>piano0142@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 235</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>20934476</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20934476</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>짐구공 헬스 PT 골프 광화문점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sujjong1015@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1389-0825</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 무교로 16 9층, 10층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://buly.kr/613HU8T</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>507</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>723</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1230</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1816876645</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1816876645</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>핏앤힐 PT&amp;헬스 약수역점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>fit2233@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1447-1774</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로 218 새움빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_TuusG</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>528</v>
+      </c>
+      <c r="R35" t="n">
+        <v>589</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1068661877</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1068661877</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>엘리트핏24 서울역점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>elitefit24@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1485-3233</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 통일로 10 연세세브란스빌딩 1층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_CxkxeBT</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>604</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>574</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1178</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1431009260</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1431009260</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>명보헬스피아</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>kindpeoplecorp@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>02-2279-7161</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 마른내로 50-1 원일빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>14</v>
+      </c>
+      <c r="R37" t="n">
+        <v>16</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>11712585</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11712585</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>시그니처짐 동대문점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>signituregym@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1498-9688</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 253 헬로우APM 8층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/signituregym</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>652</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>389</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1041</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1873078081</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1873078081</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>바디웍스 헬스 PT 신당점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bodyworks_plus@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1369-1173</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 왕십리로 407 신당파인힐하나유보라상가 2층 바디웍스</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodyworks_kr</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>457</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>107</v>
+      </c>
+      <c r="R39" t="n">
+        <v>564</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1858552812</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1858552812</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>N파크 골프앤휘트니스</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>la-lune@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>02-3789-7070</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 남대문로 30 새로나쇼핑센타 지하1층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>13</v>
+      </c>
+      <c r="R40" t="n">
+        <v>14</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>13459587</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13459587</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>하면하짐 헬스&amp;PT 신당점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>hahgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1304-1784</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로40길 14 B1 하면하짐</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xexaxhyn</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>397</v>
+      </c>
+      <c r="R41" t="n">
+        <v>523</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1406841677</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1406841677</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FITNESS101 명동점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>fitness101@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1345-0124</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 삼일대로 343 대신파이낸스센터 지하2층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://fitness101-vrtour.netlify.app/</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1018</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1261</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2279</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1025105266</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1025105266</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>베네짐 약수점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>benegym03@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>02-2252-8000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 111 5층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_benegym.yaksu</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>3796</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>311</v>
+      </c>
+      <c r="R43" t="n">
+        <v>4107</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1282104882</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1282104882</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MCTGYM 헬스&amp;PT 충무로</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>mctfitness4@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1460-1903</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로 347 1동지하2층 1호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://mctgym.com</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>109</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>185</v>
+      </c>
+      <c r="R44" t="n">
+        <v>294</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1590488695</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1590488695</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>파크짐 약수점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>parkgym_yaksu@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1483-2376</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 104 현대빌딩</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/park_yaksu</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>322</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>343</v>
+      </c>
+      <c r="R45" t="n">
+        <v>665</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>20550592</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20550592</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>서울신라호텔 피트니스클럽</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>gang1479@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>shilla.reserve@samsung.com</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02-2233-3131</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로 249 서울신라호텔 3층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.shilla.net/seoul/retreat/fnPool.do</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>545</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>64</v>
+      </c>
+      <c r="R46" t="n">
+        <v>609</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1793401463</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1793401463</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>070-4594-4730</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다동</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1372690070</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1372690070</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>겟투잇 피트니스 헬스&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sseungli12@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1316-5697</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 서소문로 89-31 지하1층, 지하2층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sseungli12</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>293</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>85</v>
+      </c>
+      <c r="R48" t="n">
+        <v>378</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1178617341</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1178617341</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>마이핏 피트니스 반월당점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>myfit3rd@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1479-0996</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>대구광역시 중구 달구벌대로 2009 2층, 3층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/myfit3rd</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>393</v>
+      </c>
+      <c r="R49" t="n">
+        <v>501</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1672974504</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1672974504</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>070-4572-4684</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로1가</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1110182025</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1110182025</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>디자인</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PT헬스장</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>itworksforme@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 태평로1가 54-3</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1478567725</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1478567725</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>헬스&amp;필라테스&amp;PT 스포짐 을지로점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>spogymmilon@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>spogymcs@hanmail.net</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1374-8202</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 삼일대로 358 신한라이프 본사 지하1층 (스타벅스 건물)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.spogym.co.kr</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>262</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1068</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1330</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>38724950</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38724950</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>좋은습관 PT STUDIO 서울역</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>goodhabit_ptstudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 만리재로 177 센트럴비발디 단지상가 1층 101호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://vo.la/K8s9f6</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>661</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>221</v>
+      </c>
+      <c r="R53" t="n">
+        <v>882</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1569459920</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1569459920</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>070-8956-3124</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 회현동1가</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1212287581</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1212287581</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>크로스핏 삼손</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>knamun@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1467-1379</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 삼일대로 363 제1,2동 제지하1층 68호,95호, 114호 이상 3개호실 전체</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/crossfitsamson</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>157</v>
+      </c>
+      <c r="R55" t="n">
+        <v>164</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1752491729</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1752491729</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>070-4572-4954</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 회현동1가</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1060990393</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1060990393</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>짐웨이 약수역점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>gymway006@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1415-0054</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로10길 21 5층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymway006</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>426</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>76</v>
+      </c>
+      <c r="R57" t="n">
+        <v>502</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2038960171</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038960171</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>골든크라운 크로스핏</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>gccf301@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1326-9667</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 정동길 8 지하1층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gccf301</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>887</v>
+      </c>
+      <c r="R58" t="n">
+        <v>966</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1889524632</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1889524632</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>헬스보이짐 앤 필라걸 을지로점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>healthboy49@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1358-8852</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 마른내로 28 B1층 헬스보이짐&amp;GDR골프인&amp;필라걸</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthboy49</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>388</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>540</v>
+      </c>
+      <c r="R59" t="n">
+        <v>928</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1881673238</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1881673238</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>070-4594-2374</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 무교동</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1017429071</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1017429071</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>F45 을지로</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>wooyeon881211@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>kingsmithfitness@gmail.com</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청계천로 100 시그니처타워 지하 1층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=com.f45training.challenge&amp;pcampaignid=web_share</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1950</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>69</v>
+      </c>
+      <c r="R61" t="n">
+        <v>2019</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1245449070</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1245449070</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>베네짐 신당점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>benegym0615@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1346-2708</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 240 지하1층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_benegym.sindang</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>2605</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>223</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2828</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1337895412</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1337895412</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>피트니스비엠 코리아나호텔점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>fitbm4@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1462-5618</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로 135 4층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitnessbm4/</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>598</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1027</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1625</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1303446863</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1303446863</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>더블에스휘트니스 명동점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>dou6le_ss@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 삼일대로 299 이화빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dou6le_ss</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>709</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1595</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2304</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1537514629</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1537514629</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>휘트니스엠 충정로점</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>fitnessm17@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1394-0801</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 서소문로 38 지하1층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessm17</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>389</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>63</v>
+      </c>
+      <c r="R65" t="n">
+        <v>452</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2042672655</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2042672655</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>팀버핏 광화문</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jhjh5508@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로 136 지하 1층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.teambutfit.com</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>34</v>
+      </c>
+      <c r="R66" t="n">
+        <v>274</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1117727301</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1117727301</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>펄스핏</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>rkduswjddus@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1313-1837</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 16 18층 펄스핏</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>77</v>
+      </c>
+      <c r="R67" t="n">
+        <v>145</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1280152729</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1280152729</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>수영장</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>성동교육문화관</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>min11ju@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>02-2231-9313</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로90길 17</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>http://www.korspo.co.kr/</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>488</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>106</v>
+      </c>
+      <c r="R68" t="n">
+        <v>594</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>34096993</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34096993</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>핏슈브 약수본점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>wkdjjs@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1391-0310</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 32 남산타운 상가2동 201호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/wkdjjs</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>34</v>
+      </c>
+      <c r="R69" t="n">
+        <v>55</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1714363732</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1714363732</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>비치바디</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>hi_gjw@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1478-1019</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 난계로 197 마블플레이스3층 비치바디</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beachbody_gym</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>8</v>
+      </c>
+      <c r="R70" t="n">
+        <v>11</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1733848127</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1733848127</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>세심한 피티 스튜디오</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>kmg09302@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1422-3416</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 409 흥인빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pt_careful</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>7</v>
+      </c>
+      <c r="R71" t="n">
+        <v>97</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1163442521</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1163442521</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>긍정체육관</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>positive_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1357-4240</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청계천로 400 롯데캐슬베네치아 상가 2층 2089호 긍정체육관</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/positive_gym</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>64</v>
+      </c>
+      <c r="R72" t="n">
+        <v>88</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1017861813</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1017861813</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>관리의기술pt 약수점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>som_pt_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1374-0256</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로7길 14 약수더시티 2층 201호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/sompt_y</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>470</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>152</v>
+      </c>
+      <c r="R73" t="n">
+        <v>622</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1688872037</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1688872037</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>이로운 퍼스널트레이닝스튜디오</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>mirkoov@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>070-4249-1212</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로31길 16 3층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mirkoov</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>11</v>
+      </c>
+      <c r="R74" t="n">
+        <v>46</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>37162566</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37162566</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>여성중심PT&amp;그룹운동 예스무브먼트</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>yes__movements@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1414-8401</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로36길 17 2층 201호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@yes.movements/</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>180</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>31</v>
+      </c>
+      <c r="R75" t="n">
+        <v>211</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1418237931</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1418237931</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>코치아카데미</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>kaosa1@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>02-2276-1718</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 삼일대로 343 b2 (피트니스101)</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kaosa1</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>18</v>
+      </c>
+      <c r="R76" t="n">
+        <v>24</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>30850587</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/30850587</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>애슬릿라이프</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>jis207@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1363-9680</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로46길 17 청계천두산위브더제니스 상가동 제2층 207호</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/athletelife.official</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>210</v>
+      </c>
+      <c r="R77" t="n">
+        <v>293</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1638258815</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1638258815</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>마이크로스튜디오 시청점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>cityhallmicro@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>owner@microstudio.kr</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1346-2162</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다동길 43 한외빌딩 지하1층 마이크로스튜디오</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://microstudio.kr</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
         <v>239</v>
       </c>
-      <c r="Q10" t="n">
-        <v>745</v>
-      </c>
-      <c r="R10" t="n">
-        <v>984</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="Q78" t="n">
+        <v>746</v>
+      </c>
+      <c r="R78" t="n">
+        <v>985</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
         <is>
           <t>1381838006</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U78" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1381838006</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>스포짐 신당역점</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>spogym18s@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1395-8487</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 447 황학아크로타워 지하1층</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spogym_sindang?igsh=NnZ4c3Qxcmgzc283</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>430</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>293</v>
+      </c>
+      <c r="R79" t="n">
+        <v>723</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1856542182</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1856542182</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>버핏그라운드 PT 광화문</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1413-0755</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로 136 서울파이낸스센터 SFC B1, B2층</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/4steppt</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>2093030344</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2093030344</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>델피피트니스컴퍼니</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>yjk7857@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1485-8072</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 137 5층</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delphi_running?igsh=a2xubWZjdjhyb3kx&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>14</v>
+      </c>
+      <c r="R81" t="n">
+        <v>30</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>2033378324</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2033378324</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>장충문화체육센터</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>stardust7784@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>02-2280-8466</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로50길 59</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>8</v>
+      </c>
+      <c r="R82" t="n">
+        <v>115</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>18054345</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18054345</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>원샵PT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>6222406a@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1359-2883</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로18길 23 1층 원샵</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_oneshop_official</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>366</v>
+      </c>
+      <c r="R83" t="n">
+        <v>598</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1045206951</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1045206951</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>조인성퍼스널트레이닝 NO.3 신당점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>joinsung_pt_pilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1488-5116</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 난계로 159 지하1층</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jo_pt03</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>282</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>344</v>
+      </c>
+      <c r="R84" t="n">
+        <v>626</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>36920061</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36920061</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>앰배서더 서울 풀만 호텔 피트니스</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>aprnovsep@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1492-3202</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로 287 앰배서더 서울 풀만 B1</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/theambassador_wellness/</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>42</v>
+      </c>
+      <c r="R85" t="n">
+        <v>57</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1455113529</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1455113529</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>파크짐 청구점</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>parkgym7744@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1376-7744</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 185 신흥빌딩 B1</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/parkgym7744</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>1188</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>634</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1822</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1262205214</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1262205214</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>다시 입히는 움직임 센터</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>rebuilding_movements@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1337-3088</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로15길 32 지하 1층 B103B호</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rebuilding_movements</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>11</v>
+      </c>
+      <c r="R87" t="n">
+        <v>30</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2079600733</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2079600733</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>롱투짐</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>longtwogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1373-3701</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로8길 70 3층 롱투짐</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/longtwogym</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>49</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>133</v>
+      </c>
+      <c r="R88" t="n">
+        <v>182</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1961897259</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1961897259</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>해핏PT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>coachj111@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1475-0642</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로9길 2 3층 301호</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/coachj111</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>84</v>
+      </c>
+      <c r="R89" t="n">
+        <v>143</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1817453072</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1817453072</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>홀리스틱 바디워크</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>holisticbodywork@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1403-4596</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로7길 32 더약수빌딩 4층 홀리스틱바디워크</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://realmovement.imweb.me/85</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>101</v>
+      </c>
+      <c r="R90" t="n">
+        <v>146</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>38301062</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38301062</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>제이현핏PT스튜디오</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>jayhyunpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1388-3491</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 107 3층</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jayhyunpt</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>62</v>
+      </c>
+      <c r="R91" t="n">
+        <v>78</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1706288434</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1706288434</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>메디앤핏 메디컬트레이닝전문센터 약수점</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>medifit2014@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>mediandfit9@gmail.com</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1323-4122</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로 168 성원빌딩 가동 5층</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>http://www.mediandfit.co.kr/</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>71</v>
+      </c>
+      <c r="R92" t="n">
+        <v>135</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1165790078</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1165790078</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>머슬인더박스 황학동베네치아점</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>nakiki700@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>02-2231-3200</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 청계천로 400 롯데캐슬베네치아메가몰 2층 2032호</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nakiki700</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>62</v>
+      </c>
+      <c r="R93" t="n">
+        <v>81</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1328981155</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1328981155</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>그로브짐 PT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>im_sung_o1988@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1340-7048</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 다산로36길 20 2층 그로브짐</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/grovegym</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>106</v>
+      </c>
+      <c r="R94" t="n">
+        <v>165</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1231410029</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1231410029</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>스포니스 약수점</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sponess_yaksu@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1310-7110</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로10길 6 3층</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sponess_yaksu</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1139</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1258</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1339455840</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1339455840</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>크로스핏알앤엘</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>crossfitrnl_su@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0507-1474-8889</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로 180 대승빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@crossfit_rnl?si=P4vSy6Nqcmiz8tEh</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>4</v>
+      </c>
+      <c r="R96" t="n">
+        <v>4</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>2062876759</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2062876759</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>키네틱 피티 스튜디오 약수점</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>kinetic_pt_seoul@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1377-5171</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 동호로14길 47 2층</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kinetic_pt_seoul</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>140</v>
+      </c>
+      <c r="R97" t="n">
+        <v>174</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1113734538</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1113734538</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>애플리케이션개발</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>스톤아이</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>shk8030@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>02-949-4206</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 퇴계로 67 AK타워 17층</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://www.da-gym.co.kr</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>2</v>
+      </c>
+      <c r="R98" t="n">
+        <v>46</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>992814340</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/992814340</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
